--- a/esyluban/examples/dev/DataTables/__beans__.xlsx
+++ b/esyluban/examples/dev/DataTables/__beans__.xlsx
@@ -763,7 +763,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
         <is>
@@ -1365,7 +1364,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="J2:P2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
